--- a/excel-files/atlas-matrices.xlsx
+++ b/excel-files/atlas-matrices.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="171">
   <si>
     <t>Reconnaissance</t>
   </si>
@@ -121,6 +121,9 @@
     <t>Publish Hallucinated Entities</t>
   </si>
   <si>
+    <t>Publish Poisoned AI Agent Tool</t>
+  </si>
+  <si>
     <t>Publish Poisoned Datasets</t>
   </si>
   <si>
@@ -154,6 +157,12 @@
     <t>Software Tools</t>
   </si>
   <si>
+    <t>Malicious Link</t>
+  </si>
+  <si>
+    <t>Poisoned AI Agent Tool</t>
+  </si>
+  <si>
     <t>AI Supply Chain Compromise</t>
   </si>
   <si>
@@ -259,6 +268,9 @@
     <t>Poison AI Model</t>
   </si>
   <si>
+    <t>Escape to Host</t>
+  </si>
+  <si>
     <t>LLM Jailbreak</t>
   </si>
   <si>
@@ -268,6 +280,9 @@
     <t>Delay Execution of LLM Instructions</t>
   </si>
   <si>
+    <t>Exploitation for Defense Evasion</t>
+  </si>
+  <si>
     <t>False RAG Entry Injection</t>
   </si>
   <si>
@@ -310,6 +325,9 @@
     <t>Credentials from AI Agent Configuration</t>
   </si>
   <si>
+    <t>Exploitation for Credential Access</t>
+  </si>
+  <si>
     <t>OS Credential Dumping</t>
   </si>
   <si>
@@ -431,6 +449,9 @@
   </si>
   <si>
     <t>Use Pre-Trained Model</t>
+  </si>
+  <si>
+    <t>AI Agent</t>
   </si>
   <si>
     <t>AI Service API</t>
@@ -512,7 +533,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -523,14 +544,6 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -590,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
@@ -600,9 +613,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -901,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -948,7 +958,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="3"/>
-      <c r="G1" s="4" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -959,14 +969,14 @@
         <v>5</v>
       </c>
       <c r="K1" s="3"/>
-      <c r="L1" s="4" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="N1" s="3"/>
-      <c r="O1" s="4" t="s">
+      <c r="O1" t="s">
         <v>8</v>
       </c>
       <c r="P1" s="3" t="s">
@@ -985,7 +995,7 @@
         <v>12</v>
       </c>
       <c r="W1" s="3"/>
-      <c r="X1" s="4" t="s">
+      <c r="X1" t="s">
         <v>13</v>
       </c>
       <c r="Y1" s="3" t="s">
@@ -1001,232 +1011,235 @@
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L2" t="s">
-        <v>63</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O2" t="s">
-        <v>96</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="S2" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="V2" s="5" t="s">
         <v>126</v>
       </c>
+      <c r="V2" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="W2" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="X2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="5"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="E3" s="4"/>
       <c r="F3" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="J3" s="4"/>
       <c r="K3" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="O3" t="s">
-        <v>97</v>
-      </c>
-      <c r="P3" s="5" t="s">
         <v>102</v>
       </c>
+      <c r="P3" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="Q3" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="V3" s="5"/>
+        <v>130</v>
+      </c>
+      <c r="V3" s="4"/>
       <c r="W3" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="X3" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>149</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="5"/>
+        <v>42</v>
+      </c>
+      <c r="E4" s="4"/>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L4" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O4" t="s">
-        <v>98</v>
-      </c>
-      <c r="P4" s="5"/>
+        <v>103</v>
+      </c>
+      <c r="P4" s="4"/>
       <c r="Q4" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="T4" s="5"/>
+        <v>117</v>
+      </c>
+      <c r="T4" s="4"/>
       <c r="U4" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V4" s="5"/>
+        <v>131</v>
+      </c>
+      <c r="V4" s="4"/>
       <c r="W4" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y4" s="5"/>
+        <v>139</v>
+      </c>
+      <c r="X4" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y4" s="4"/>
       <c r="Z4" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="5"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="E5" s="4"/>
       <c r="F5" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
+      </c>
+      <c r="L5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="O5" t="s">
-        <v>99</v>
-      </c>
-      <c r="P5" s="5"/>
+        <v>104</v>
+      </c>
+      <c r="P5" s="4"/>
       <c r="Q5" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="V5" s="5"/>
+        <v>128</v>
+      </c>
+      <c r="V5" s="4"/>
       <c r="W5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y5" s="5"/>
+        <v>140</v>
+      </c>
+      <c r="Y5" s="4"/>
       <c r="Z5" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -1237,52 +1250,54 @@
         <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>66</v>
+        <v>50</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="M6" s="5"/>
+        <v>82</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="N6" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="O6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="V6" s="5"/>
+        <v>129</v>
+      </c>
+      <c r="V6" s="4"/>
       <c r="W6" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:28">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1292,38 +1307,41 @@
         <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="5"/>
+        <v>51</v>
+      </c>
+      <c r="H7" s="4"/>
       <c r="I7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J7" s="5"/>
+        <v>72</v>
+      </c>
+      <c r="J7" s="4"/>
       <c r="K7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M7" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="M7" s="4"/>
       <c r="N7" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
+      </c>
+      <c r="O7" t="s">
+        <v>106</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="V7" s="5" t="s">
-        <v>127</v>
+        <v>110</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:28">
-      <c r="A8" s="5"/>
+      <c r="A8" s="4"/>
       <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1331,110 +1349,111 @@
         <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
+      </c>
+      <c r="M8" s="4"/>
+      <c r="N8" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="V8" s="5"/>
+        <v>111</v>
+      </c>
+      <c r="V8" s="4"/>
       <c r="W8" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA8" s="5" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:28">
-      <c r="A9" s="5"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>33</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="V9" s="5"/>
+        <v>119</v>
+      </c>
+      <c r="V9" s="4"/>
       <c r="W9" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA9" s="5"/>
+        <v>157</v>
+      </c>
+      <c r="AA9" s="4"/>
       <c r="AB9" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="5"/>
+      <c r="C10" s="4"/>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>107</v>
+        <v>85</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA10" s="5"/>
+        <v>134</v>
+      </c>
+      <c r="AA10" s="4"/>
       <c r="AB10" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -1445,24 +1464,24 @@
         <v>33</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="P11" s="5"/>
+        <v>91</v>
+      </c>
+      <c r="P11" s="4"/>
       <c r="Q11" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA11" s="5"/>
+        <v>135</v>
+      </c>
+      <c r="AA11" s="4"/>
       <c r="AB11" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:28">
@@ -1470,82 +1489,103 @@
         <v>34</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>108</v>
+        <v>92</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="V12" s="5" t="s">
-        <v>74</v>
+        <v>122</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA12" s="5"/>
+        <v>82</v>
+      </c>
+      <c r="AA12" s="4"/>
       <c r="AB12" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:28">
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="D13" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="M13" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="P13" s="5"/>
+        <v>93</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="P13" s="4"/>
       <c r="Q13" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="V13" s="5"/>
+        <v>123</v>
+      </c>
+      <c r="V13" s="4"/>
       <c r="W13" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:28">
-      <c r="C14" s="1" t="s">
-        <v>36</v>
+      <c r="C14" s="4"/>
+      <c r="D14" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="P14" s="5"/>
+        <v>94</v>
+      </c>
+      <c r="P14" s="4"/>
       <c r="Q14" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:28">
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:28">
       <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="1" t="s">
         <v>38</v>
       </c>
     </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E2:E5"/>
     <mergeCell ref="E1:F1"/>
@@ -1554,7 +1594,7 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="M5:M7"/>
+    <mergeCell ref="M6:M8"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P3:P5"/>
     <mergeCell ref="P10:P11"/>

--- a/excel-files/atlas-matrices.xlsx
+++ b/excel-files/atlas-matrices.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="183">
   <si>
     <t>Reconnaissance</t>
   </si>
@@ -244,6 +244,9 @@
     <t>AI Agent Tool Data Poisoning</t>
   </si>
   <si>
+    <t>AI Agent Tool Poisoning</t>
+  </si>
+  <si>
     <t>LLM Prompt Self-Replication</t>
   </si>
   <si>
@@ -262,6 +265,21 @@
     <t>Thread</t>
   </si>
   <si>
+    <t>AI Agent Tool</t>
+  </si>
+  <si>
+    <t>Agentic Resource Consumption</t>
+  </si>
+  <si>
+    <t>Call Chains</t>
+  </si>
+  <si>
+    <t>Excessive Queries</t>
+  </si>
+  <si>
+    <t>Resource-Intensive Queries</t>
+  </si>
+  <si>
     <t>Modify AI Model Architecture</t>
   </si>
   <si>
@@ -274,6 +292,12 @@
     <t>LLM Jailbreak</t>
   </si>
   <si>
+    <t>AI Supply Chain Reputation Inflation</t>
+  </si>
+  <si>
+    <t>AI Supply Chain Rug Pull</t>
+  </si>
+  <si>
     <t>Corrupt AI Model</t>
   </si>
   <si>
@@ -508,6 +532,9 @@
     <t>External Harms</t>
   </si>
   <si>
+    <t>Machine Compromise</t>
+  </si>
+  <si>
     <t>Spamming AI System with Chaff Data</t>
   </si>
   <si>
@@ -527,13 +554,22 @@
   </si>
   <si>
     <t>User Harm</t>
+  </si>
+  <si>
+    <t>AI Artifacts</t>
+  </si>
+  <si>
+    <t>AI Service Proxies</t>
+  </si>
+  <si>
+    <t>Local AI Agent</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -544,6 +580,14 @@
     <font>
       <b/>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -603,7 +647,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
@@ -613,6 +657,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -958,7 +1005,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="3"/>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -969,14 +1016,14 @@
         <v>5</v>
       </c>
       <c r="K1" s="3"/>
-      <c r="L1" t="s">
+      <c r="L1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="N1" s="3"/>
-      <c r="O1" t="s">
+      <c r="O1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="P1" s="3" t="s">
@@ -995,7 +1042,7 @@
         <v>12</v>
       </c>
       <c r="W1" s="3"/>
-      <c r="X1" t="s">
+      <c r="X1" s="4" t="s">
         <v>13</v>
       </c>
       <c r="Y1" s="3" t="s">
@@ -1011,13 +1058,13 @@
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>49</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -1029,23 +1076,23 @@
       <c r="H2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>74</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s">
         <v>66</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="O2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>53</v>
@@ -1054,33 +1101,33 @@
         <v>60</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="X2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="5"/>
       <c r="D3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="5"/>
       <c r="F3" s="2" t="s">
         <v>57</v>
       </c>
@@ -1090,65 +1137,62 @@
       <c r="H3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="5"/>
       <c r="K3" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="V3" s="4"/>
+        <v>138</v>
+      </c>
+      <c r="V3" s="5"/>
       <c r="W3" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="X3" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="5"/>
       <c r="F4" s="2" t="s">
         <v>58</v>
       </c>
@@ -1162,46 +1206,46 @@
         <v>75</v>
       </c>
       <c r="L4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="O4" t="s">
-        <v>103</v>
-      </c>
-      <c r="P4" s="4"/>
+        <v>111</v>
+      </c>
+      <c r="P4" s="5"/>
       <c r="Q4" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T4" s="4"/>
+        <v>125</v>
+      </c>
+      <c r="T4" s="5"/>
       <c r="U4" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="V4" s="4"/>
+        <v>139</v>
+      </c>
+      <c r="V4" s="5"/>
       <c r="W4" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="X4" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y4" s="4"/>
+        <v>155</v>
+      </c>
+      <c r="Y4" s="5"/>
       <c r="Z4" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="5"/>
       <c r="F5" s="2" t="s">
         <v>59</v>
       </c>
@@ -1211,35 +1255,41 @@
       <c r="H5" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="5" t="s">
         <v>76</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="L5" t="s">
         <v>55</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="O5" t="s">
-        <v>104</v>
-      </c>
-      <c r="P5" s="4"/>
+        <v>112</v>
+      </c>
+      <c r="P5" s="5"/>
       <c r="Q5" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="V5" s="4"/>
+        <v>136</v>
+      </c>
+      <c r="V5" s="5"/>
       <c r="W5" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y5" s="4"/>
+        <v>148</v>
+      </c>
+      <c r="Y5" s="5"/>
       <c r="Z5" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -1255,49 +1305,44 @@
       <c r="E6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>69</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>77</v>
-      </c>
+      <c r="J6" s="5"/>
       <c r="K6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="O6" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="V6" s="4"/>
+        <v>137</v>
+      </c>
+      <c r="V6" s="5"/>
       <c r="W6" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:28">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1309,39 +1354,38 @@
       <c r="E7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J7" s="4"/>
+      <c r="J7" s="5"/>
       <c r="K7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="M7" s="4"/>
-      <c r="N7" s="2" t="s">
-        <v>98</v>
+        <v>85</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="O7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="V7" s="4" t="s">
-        <v>133</v>
+        <v>118</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="AA7" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:28">
-      <c r="A8" s="4"/>
+      <c r="A8" s="5"/>
       <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1357,36 +1401,39 @@
       <c r="I8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>97</v>
+      </c>
       <c r="N8" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="V8" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="V8" s="5"/>
       <c r="W8" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA8" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:28">
-      <c r="A9" s="4"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -1398,38 +1445,40 @@
       <c r="F9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>90</v>
+      <c r="J9" s="5"/>
+      <c r="K9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="V9" s="4"/>
+        <v>127</v>
+      </c>
+      <c r="V9" s="5"/>
       <c r="W9" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AA9" s="4"/>
+        <v>165</v>
+      </c>
+      <c r="AA9" s="5"/>
       <c r="AB9" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="2" t="s">
         <v>46</v>
       </c>
@@ -1437,23 +1486,24 @@
         <v>54</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>113</v>
+        <v>77</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA10" s="4"/>
+        <v>142</v>
+      </c>
+      <c r="AA10" s="5"/>
       <c r="AB10" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -1466,120 +1516,159 @@
       <c r="E11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>79</v>
+      <c r="J11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P11" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="P11" s="5"/>
       <c r="Q11" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA11" s="4"/>
+        <v>143</v>
+      </c>
+      <c r="AA11" s="5"/>
       <c r="AB11" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:28">
       <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="M12" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>114</v>
+        <v>91</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="V12" s="4" t="s">
-        <v>77</v>
+        <v>130</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA12" s="4"/>
+        <v>88</v>
+      </c>
+      <c r="AA12" s="5"/>
       <c r="AB12" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:28">
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="J13" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="M13" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="P13" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="P13" s="5"/>
       <c r="Q13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="V13" s="4"/>
+        <v>131</v>
+      </c>
+      <c r="V13" s="5"/>
       <c r="W13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA13" s="1" t="s">
-        <v>164</v>
+        <v>89</v>
+      </c>
+      <c r="AA13" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:28">
-      <c r="C14" s="4"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="J14" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="M14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="P14" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="P14" s="5"/>
       <c r="Q14" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
+      </c>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:28">
       <c r="C15" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="J15" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="M15" s="1" t="s">
-        <v>78</v>
+        <v>101</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
+      </c>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:28">
       <c r="C16" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="J16" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="M16" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>173</v>
       </c>
     </row>
-    <row r="17" spans="3:3">
+    <row r="17" spans="3:13">
       <c r="C17" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="M17" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="18" spans="3:3">
+    <row r="18" spans="3:13">
       <c r="C18" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="M18" s="1" t="s">
+        <v>103</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="33">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C2:C3"/>
@@ -1592,9 +1681,10 @@
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J2:J3"/>
-    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J5:J9"/>
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="M8:M10"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P3:P5"/>
     <mergeCell ref="P10:P11"/>
@@ -1610,6 +1700,7 @@
     <mergeCell ref="Y3:Y5"/>
     <mergeCell ref="Y1:Z1"/>
     <mergeCell ref="AA8:AA12"/>
+    <mergeCell ref="AA13:AA15"/>
     <mergeCell ref="AA1:AB1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/atlas-matrices.xlsx
+++ b/excel-files/atlas-matrices.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="186">
   <si>
     <t>Reconnaissance</t>
   </si>
@@ -97,6 +97,9 @@
     <t>Technical Blogs</t>
   </si>
   <si>
+    <t>Code Repositories</t>
+  </si>
+  <si>
     <t>Acquire Infrastructure</t>
   </si>
   <si>
@@ -139,9 +142,24 @@
     <t>AI Development Workspaces</t>
   </si>
   <si>
+    <t>AI Service Proxies</t>
+  </si>
+  <si>
     <t>Consumer Hardware</t>
   </si>
   <si>
+    <t>Domains</t>
+  </si>
+  <si>
+    <t>Physical Countermeasures</t>
+  </si>
+  <si>
+    <t>Serverless</t>
+  </si>
+  <si>
+    <t>AI Agent Configuration</t>
+  </si>
+  <si>
     <t>Datasets</t>
   </si>
   <si>
@@ -154,87 +172,105 @@
     <t>Adversarial AI Attack Implementations</t>
   </si>
   <si>
+    <t>Generative AI</t>
+  </si>
+  <si>
     <t>Software Tools</t>
   </si>
   <si>
+    <t>AI Supply Chain Compromise</t>
+  </si>
+  <si>
+    <t>Drive-by Compromise</t>
+  </si>
+  <si>
+    <t>Evade AI Model</t>
+  </si>
+  <si>
+    <t>Exploit Public-Facing Application</t>
+  </si>
+  <si>
+    <t>Phishing</t>
+  </si>
+  <si>
+    <t>Prompt Infiltration via Public-Facing Application</t>
+  </si>
+  <si>
+    <t>Valid Accounts</t>
+  </si>
+  <si>
+    <t>AI Agent Tool</t>
+  </si>
+  <si>
+    <t>AI Software</t>
+  </si>
+  <si>
+    <t>Container Registry</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Hardware</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Deepfake-Assisted Phishing</t>
+  </si>
+  <si>
+    <t>Spearphishing via Social Engineering LLM</t>
+  </si>
+  <si>
+    <t>AI Model Inference API Access</t>
+  </si>
+  <si>
+    <t>AI-Enabled Product or Service</t>
+  </si>
+  <si>
+    <t>Full AI Model Access</t>
+  </si>
+  <si>
+    <t>Physical Environment Access</t>
+  </si>
+  <si>
+    <t>AI Agent Clickbait</t>
+  </si>
+  <si>
+    <t>AI Agent Tool Invocation</t>
+  </si>
+  <si>
+    <t>Command and Scripting Interpreter</t>
+  </si>
+  <si>
+    <t>Deploy AI Agent</t>
+  </si>
+  <si>
+    <t>LLM Prompt Injection</t>
+  </si>
+  <si>
+    <t>User Execution</t>
+  </si>
+  <si>
+    <t>Direct</t>
+  </si>
+  <si>
+    <t>Indirect</t>
+  </si>
+  <si>
+    <t>Triggered</t>
+  </si>
+  <si>
     <t>Malicious Link</t>
   </si>
   <si>
+    <t>Malicious Package</t>
+  </si>
+  <si>
     <t>Poisoned AI Agent Tool</t>
   </si>
   <si>
-    <t>AI Supply Chain Compromise</t>
-  </si>
-  <si>
-    <t>Drive-by Compromise</t>
-  </si>
-  <si>
-    <t>Evade AI Model</t>
-  </si>
-  <si>
-    <t>Exploit Public-Facing Application</t>
-  </si>
-  <si>
-    <t>Phishing</t>
-  </si>
-  <si>
-    <t>Prompt Infiltration via Public-Facing Application</t>
-  </si>
-  <si>
-    <t>Valid Accounts</t>
-  </si>
-  <si>
-    <t>AI Software</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Hardware</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Spearphishing via Social Engineering LLM</t>
-  </si>
-  <si>
-    <t>AI Model Inference API Access</t>
-  </si>
-  <si>
-    <t>AI-Enabled Product or Service</t>
-  </si>
-  <si>
-    <t>Full AI Model Access</t>
-  </si>
-  <si>
-    <t>Physical Environment Access</t>
-  </si>
-  <si>
-    <t>AI Agent Clickbait</t>
-  </si>
-  <si>
-    <t>AI Agent Tool Invocation</t>
-  </si>
-  <si>
-    <t>Command and Scripting Interpreter</t>
-  </si>
-  <si>
-    <t>Deploy AI Agent</t>
-  </si>
-  <si>
-    <t>LLM Prompt Injection</t>
-  </si>
-  <si>
-    <t>User Execution</t>
-  </si>
-  <si>
-    <t>Direct</t>
-  </si>
-  <si>
-    <t>Indirect</t>
-  </si>
-  <si>
     <t>Unsafe AI Artifacts</t>
   </si>
   <si>
@@ -265,282 +301,258 @@
     <t>Thread</t>
   </si>
   <si>
-    <t>AI Agent Tool</t>
+    <t>Embed Malware</t>
+  </si>
+  <si>
+    <t>Modify AI Model Architecture</t>
+  </si>
+  <si>
+    <t>Poison AI Model</t>
+  </si>
+  <si>
+    <t>Escape to Host</t>
+  </si>
+  <si>
+    <t>LLM Jailbreak</t>
+  </si>
+  <si>
+    <t>AI Supply Chain Reputation Inflation</t>
+  </si>
+  <si>
+    <t>AI Supply Chain Rug Pull</t>
+  </si>
+  <si>
+    <t>Corrupt AI Model</t>
+  </si>
+  <si>
+    <t>Delay Execution of LLM Instructions</t>
+  </si>
+  <si>
+    <t>Exploitation for Defense Evasion</t>
+  </si>
+  <si>
+    <t>False RAG Entry Injection</t>
+  </si>
+  <si>
+    <t>Impersonation</t>
+  </si>
+  <si>
+    <t>LLM Prompt Obfuscation</t>
+  </si>
+  <si>
+    <t>LLM Trusted Output Components Manipulation</t>
+  </si>
+  <si>
+    <t>Manipulate User LLM Chat History</t>
+  </si>
+  <si>
+    <t>Masquerading</t>
+  </si>
+  <si>
+    <t>Virtualization/Sandbox Evasion</t>
+  </si>
+  <si>
+    <t>Citations</t>
+  </si>
+  <si>
+    <t>AI Agent Tool Credential Harvesting</t>
+  </si>
+  <si>
+    <t>Credentials from AI Agent Configuration</t>
+  </si>
+  <si>
+    <t>Exploitation for Credential Access</t>
+  </si>
+  <si>
+    <t>OS Credential Dumping</t>
+  </si>
+  <si>
+    <t>RAG Credential Harvesting</t>
+  </si>
+  <si>
+    <t>Unsecured Credentials</t>
+  </si>
+  <si>
+    <t>Cloud Service Discovery</t>
+  </si>
+  <si>
+    <t>Discover AI Agent Configuration</t>
+  </si>
+  <si>
+    <t>Discover AI Artifacts</t>
+  </si>
+  <si>
+    <t>Discover AI Model Family</t>
+  </si>
+  <si>
+    <t>Discover AI Model Ontology</t>
+  </si>
+  <si>
+    <t>Discover AI Model Outputs</t>
+  </si>
+  <si>
+    <t>Discover LLM Hallucinations</t>
+  </si>
+  <si>
+    <t>Discover LLM System Information</t>
+  </si>
+  <si>
+    <t>Process Discovery</t>
+  </si>
+  <si>
+    <t>Activation Triggers</t>
+  </si>
+  <si>
+    <t>Call Chains</t>
+  </si>
+  <si>
+    <t>Embedded Knowledge</t>
+  </si>
+  <si>
+    <t>Tool Definitions</t>
+  </si>
+  <si>
+    <t>Special Character Sets</t>
+  </si>
+  <si>
+    <t>System Instruction Keywords</t>
+  </si>
+  <si>
+    <t>System Prompt</t>
+  </si>
+  <si>
+    <t>Use Alternate Authentication Material</t>
+  </si>
+  <si>
+    <t>Application Access Token</t>
+  </si>
+  <si>
+    <t>AI Artifact Collection</t>
+  </si>
+  <si>
+    <t>Data from AI Services</t>
+  </si>
+  <si>
+    <t>Data from Information Repositories</t>
+  </si>
+  <si>
+    <t>Data from Local System</t>
+  </si>
+  <si>
+    <t>AI Agent Tools</t>
+  </si>
+  <si>
+    <t>RAG Databases</t>
+  </si>
+  <si>
+    <t>Craft Adversarial Data</t>
+  </si>
+  <si>
+    <t>Create Proxy AI Model</t>
+  </si>
+  <si>
+    <t>Generate Deepfakes</t>
+  </si>
+  <si>
+    <t>Generate Malicious Commands</t>
+  </si>
+  <si>
+    <t>Verify Attack</t>
+  </si>
+  <si>
+    <t>Black-Box Optimization</t>
+  </si>
+  <si>
+    <t>Black-Box Transfer</t>
+  </si>
+  <si>
+    <t>Insert Backdoor Trigger</t>
+  </si>
+  <si>
+    <t>Manual Modification</t>
+  </si>
+  <si>
+    <t>White-Box Optimization</t>
+  </si>
+  <si>
+    <t>Train Proxy via Gathered AI Artifacts</t>
+  </si>
+  <si>
+    <t>Train Proxy via Replication</t>
+  </si>
+  <si>
+    <t>Use Pre-Trained Model</t>
+  </si>
+  <si>
+    <t>AI Agent</t>
+  </si>
+  <si>
+    <t>AI Service API</t>
+  </si>
+  <si>
+    <t>Reverse Shell</t>
+  </si>
+  <si>
+    <t>Exfiltration via AI Agent Tool Invocation</t>
+  </si>
+  <si>
+    <t>Exfiltration via AI Inference API</t>
+  </si>
+  <si>
+    <t>Exfiltration via Cyber Means</t>
+  </si>
+  <si>
+    <t>Extract LLM System Prompt</t>
+  </si>
+  <si>
+    <t>LLM Data Leakage</t>
+  </si>
+  <si>
+    <t>LLM Response Rendering</t>
+  </si>
+  <si>
+    <t>Extract AI Model</t>
+  </si>
+  <si>
+    <t>Infer Training Data Membership</t>
+  </si>
+  <si>
+    <t>Invert AI Model</t>
+  </si>
+  <si>
+    <t>Cost Harvesting</t>
+  </si>
+  <si>
+    <t>Data Destruction via AI Agent Tool Invocation</t>
+  </si>
+  <si>
+    <t>Denial of AI Service</t>
+  </si>
+  <si>
+    <t>Erode AI Model Integrity</t>
+  </si>
+  <si>
+    <t>Erode Dataset Integrity</t>
+  </si>
+  <si>
+    <t>External Harms</t>
+  </si>
+  <si>
+    <t>Machine Compromise</t>
+  </si>
+  <si>
+    <t>Spamming AI System with Chaff Data</t>
   </si>
   <si>
     <t>Agentic Resource Consumption</t>
   </si>
   <si>
-    <t>Call Chains</t>
-  </si>
-  <si>
     <t>Excessive Queries</t>
   </si>
   <si>
     <t>Resource-Intensive Queries</t>
   </si>
   <si>
-    <t>Modify AI Model Architecture</t>
-  </si>
-  <si>
-    <t>Poison AI Model</t>
-  </si>
-  <si>
-    <t>Escape to Host</t>
-  </si>
-  <si>
-    <t>LLM Jailbreak</t>
-  </si>
-  <si>
-    <t>AI Supply Chain Reputation Inflation</t>
-  </si>
-  <si>
-    <t>AI Supply Chain Rug Pull</t>
-  </si>
-  <si>
-    <t>Corrupt AI Model</t>
-  </si>
-  <si>
-    <t>Delay Execution of LLM Instructions</t>
-  </si>
-  <si>
-    <t>Exploitation for Defense Evasion</t>
-  </si>
-  <si>
-    <t>False RAG Entry Injection</t>
-  </si>
-  <si>
-    <t>Impersonation</t>
-  </si>
-  <si>
-    <t>LLM Prompt Obfuscation</t>
-  </si>
-  <si>
-    <t>LLM Trusted Output Components Manipulation</t>
-  </si>
-  <si>
-    <t>Manipulate User LLM Chat History</t>
-  </si>
-  <si>
-    <t>Masquerading</t>
-  </si>
-  <si>
-    <t>Virtualization/Sandbox Evasion</t>
-  </si>
-  <si>
-    <t>Triggered</t>
-  </si>
-  <si>
-    <t>Citations</t>
-  </si>
-  <si>
-    <t>Container Registry</t>
-  </si>
-  <si>
-    <t>Embed Malware</t>
-  </si>
-  <si>
-    <t>Application Access Token</t>
-  </si>
-  <si>
-    <t>AI Agent Tool Credential Harvesting</t>
-  </si>
-  <si>
-    <t>Credentials from AI Agent Configuration</t>
-  </si>
-  <si>
-    <t>Exploitation for Credential Access</t>
-  </si>
-  <si>
-    <t>OS Credential Dumping</t>
-  </si>
-  <si>
-    <t>RAG Credential Harvesting</t>
-  </si>
-  <si>
-    <t>Unsecured Credentials</t>
-  </si>
-  <si>
-    <t>Cloud Service Discovery</t>
-  </si>
-  <si>
-    <t>Discover AI Agent Configuration</t>
-  </si>
-  <si>
-    <t>Discover AI Artifacts</t>
-  </si>
-  <si>
-    <t>Discover AI Model Family</t>
-  </si>
-  <si>
-    <t>Discover AI Model Ontology</t>
-  </si>
-  <si>
-    <t>Discover AI Model Outputs</t>
-  </si>
-  <si>
-    <t>Discover LLM Hallucinations</t>
-  </si>
-  <si>
-    <t>Discover LLM System Information</t>
-  </si>
-  <si>
-    <t>Process Discovery</t>
-  </si>
-  <si>
-    <t>Activation Triggers</t>
-  </si>
-  <si>
-    <t>Embedded Knowledge</t>
-  </si>
-  <si>
-    <t>Tool Definitions</t>
-  </si>
-  <si>
-    <t>Generative AI</t>
-  </si>
-  <si>
-    <t>Domains</t>
-  </si>
-  <si>
-    <t>Physical Countermeasures</t>
-  </si>
-  <si>
-    <t>Special Character Sets</t>
-  </si>
-  <si>
-    <t>System Instruction Keywords</t>
-  </si>
-  <si>
-    <t>System Prompt</t>
-  </si>
-  <si>
-    <t>Use Alternate Authentication Material</t>
-  </si>
-  <si>
-    <t>AI Artifact Collection</t>
-  </si>
-  <si>
-    <t>Data from AI Services</t>
-  </si>
-  <si>
-    <t>Data from Information Repositories</t>
-  </si>
-  <si>
-    <t>Data from Local System</t>
-  </si>
-  <si>
-    <t>AI Agent Tools</t>
-  </si>
-  <si>
-    <t>RAG Databases</t>
-  </si>
-  <si>
-    <t>Craft Adversarial Data</t>
-  </si>
-  <si>
-    <t>Create Proxy AI Model</t>
-  </si>
-  <si>
-    <t>Generate Deepfakes</t>
-  </si>
-  <si>
-    <t>Generate Malicious Commands</t>
-  </si>
-  <si>
-    <t>Verify Attack</t>
-  </si>
-  <si>
-    <t>Black-Box Optimization</t>
-  </si>
-  <si>
-    <t>Black-Box Transfer</t>
-  </si>
-  <si>
-    <t>Insert Backdoor Trigger</t>
-  </si>
-  <si>
-    <t>Manual Modification</t>
-  </si>
-  <si>
-    <t>White-Box Optimization</t>
-  </si>
-  <si>
-    <t>Train Proxy via Gathered AI Artifacts</t>
-  </si>
-  <si>
-    <t>Train Proxy via Replication</t>
-  </si>
-  <si>
-    <t>Use Pre-Trained Model</t>
-  </si>
-  <si>
-    <t>AI Agent</t>
-  </si>
-  <si>
-    <t>AI Service API</t>
-  </si>
-  <si>
-    <t>Reverse Shell</t>
-  </si>
-  <si>
-    <t>Exfiltration via AI Agent Tool Invocation</t>
-  </si>
-  <si>
-    <t>Exfiltration via AI Inference API</t>
-  </si>
-  <si>
-    <t>Exfiltration via Cyber Means</t>
-  </si>
-  <si>
-    <t>Extract LLM System Prompt</t>
-  </si>
-  <si>
-    <t>LLM Data Leakage</t>
-  </si>
-  <si>
-    <t>LLM Response Rendering</t>
-  </si>
-  <si>
-    <t>Extract AI Model</t>
-  </si>
-  <si>
-    <t>Infer Training Data Membership</t>
-  </si>
-  <si>
-    <t>Invert AI Model</t>
-  </si>
-  <si>
-    <t>Serverless</t>
-  </si>
-  <si>
-    <t>Cost Harvesting</t>
-  </si>
-  <si>
-    <t>Data Destruction via AI Agent Tool Invocation</t>
-  </si>
-  <si>
-    <t>Denial of AI Service</t>
-  </si>
-  <si>
-    <t>Erode AI Model Integrity</t>
-  </si>
-  <si>
-    <t>Erode Dataset Integrity</t>
-  </si>
-  <si>
-    <t>External Harms</t>
-  </si>
-  <si>
-    <t>Machine Compromise</t>
-  </si>
-  <si>
-    <t>Spamming AI System with Chaff Data</t>
-  </si>
-  <si>
-    <t>Malicious Package</t>
-  </si>
-  <si>
     <t>AI Intellectual Property Theft</t>
   </si>
   <si>
@@ -557,9 +569,6 @@
   </si>
   <si>
     <t>AI Artifacts</t>
-  </si>
-  <si>
-    <t>AI Service Proxies</t>
   </si>
   <si>
     <t>Local AI Agent</t>
@@ -958,7 +967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB18"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -1059,64 +1068,67 @@
         <v>16</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J2" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L2" t="s">
         <v>74</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L2" t="s">
-        <v>66</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="O2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>53</v>
+        <v>119</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:28">
@@ -1125,116 +1137,123 @@
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="O3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
+      </c>
+      <c r="R3" s="5"/>
+      <c r="S3" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="V3" s="5"/>
       <c r="W3" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="X3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
+      </c>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="C4" s="5"/>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="L4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="O4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="P4" s="5"/>
       <c r="Q4" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="T4" s="5"/>
       <c r="U4" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="V4" s="5"/>
       <c r="W4" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="X4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y4" s="5"/>
       <c r="Z4" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
+      </c>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="2" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:28">
@@ -1243,50 +1262,44 @@
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J5" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>83</v>
+      <c r="J5" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="P5" s="5"/>
       <c r="Q5" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="V5" s="5"/>
       <c r="W5" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Y5" s="5"/>
       <c r="Z5" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AA5" s="1" t="s">
         <v>169</v>
@@ -1296,49 +1309,45 @@
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="C6" s="5"/>
       <c r="D6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O6" t="s">
-        <v>113</v>
-      </c>
-      <c r="P6" s="1" t="s">
         <v>117</v>
       </c>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="T6" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="V6" s="5"/>
       <c r="W6" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AA6" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="AB6" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -1348,40 +1357,44 @@
       <c r="B7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>51</v>
+      <c r="C7" s="5"/>
+      <c r="D7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J7" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="K7" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="O7" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>51</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:28">
@@ -1389,43 +1402,38 @@
       <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>31</v>
+      <c r="C8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>70</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="H8" s="5"/>
       <c r="I8" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="N8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>105</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="V8" s="5"/>
       <c r="W8" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA8" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>175</v>
+        <v>163</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -1433,77 +1441,75 @@
       <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>32</v>
-      </c>
+      <c r="C9" s="5"/>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>106</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="V9" s="5"/>
       <c r="W9" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA9" s="5"/>
-      <c r="AB9" s="2" t="s">
-        <v>176</v>
+        <v>164</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C10" s="5"/>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>128</v>
+        <v>91</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA10" s="5"/>
+        <v>145</v>
+      </c>
+      <c r="AA10" s="5" t="s">
+        <v>173</v>
+      </c>
       <c r="AB10" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -1511,196 +1517,234 @@
         <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>88</v>
+        <v>30</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="2" t="s">
-        <v>129</v>
+        <v>107</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AA11" s="5"/>
       <c r="AB11" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:28">
       <c r="C12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="2" t="s">
-        <v>89</v>
+        <v>31</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>91</v>
+        <v>108</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="AA12" s="5"/>
       <c r="AB12" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:28">
-      <c r="C13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>47</v>
+      <c r="C13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="P13" s="5"/>
       <c r="Q13" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="V13" s="5"/>
       <c r="W13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA13" s="5" t="s">
-        <v>172</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AA13" s="5"/>
       <c r="AB13" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:28">
-      <c r="C14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P14" s="5"/>
       <c r="Q14" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
+      </c>
+      <c r="V14" s="5"/>
+      <c r="W14" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="AA14" s="5"/>
       <c r="AB14" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:28">
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="5"/>
+      <c r="D15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA15" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB15" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
+      <c r="C16" s="5"/>
+      <c r="D16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA16" s="5"/>
+      <c r="AB16" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="17" spans="3:27">
+      <c r="C17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27">
+      <c r="C18" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27">
+      <c r="C19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA15" s="5"/>
-      <c r="AB15" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28">
-      <c r="C16" s="1" t="s">
+    </row>
+    <row r="20" spans="3:27">
+      <c r="C20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA16" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="3:13">
-      <c r="C17" s="1" t="s">
+    </row>
+    <row r="21" spans="3:27">
+      <c r="C21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M17" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="3:13">
-      <c r="C18" s="1" t="s">
+    </row>
+    <row r="22" spans="3:27">
+      <c r="C22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>103</v>
+    </row>
+    <row r="23" spans="3:27">
+      <c r="C23" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="33">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C2:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C14:C16"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E11:E12"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="H9:H12"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J2:J3"/>
-    <mergeCell ref="J5:J9"/>
-    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J7:J9"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="M8:M10"/>
     <mergeCell ref="M1:N1"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="P3:P6"/>
     <mergeCell ref="P12:P14"/>
     <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R2:R3"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="V2:V6"/>
     <mergeCell ref="V7:V9"/>
-    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="V12:V14"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="Y3:Y5"/>
     <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA8:AA12"/>
-    <mergeCell ref="AA13:AA15"/>
+    <mergeCell ref="AA2:AA4"/>
+    <mergeCell ref="AA10:AA14"/>
+    <mergeCell ref="AA15:AA16"/>
     <mergeCell ref="AA1:AB1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
